--- a/artfynd/A 45224-2024 artfynd.xlsx
+++ b/artfynd/A 45224-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4899152</v>
+        <v>6776533</v>
       </c>
       <c r="B2" t="n">
-        <v>97308</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222467</v>
+        <v>504</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gräsull</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Eriophorum latifolium</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Hoppe</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>500162.943566215</v>
+        <v>500735</v>
       </c>
       <c r="R2" t="n">
-        <v>7026263.997187783</v>
+        <v>7026456</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,24 +743,14 @@
           <t>2012-09-10</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2012-09-10</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>rikkärrskant</t>
+          <t>6 bestånd, totalt ca 50 pl. inom ca 100 m2.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,11 +761,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Tallskog - barrblandskog</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -801,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>4964589</v>
+        <v>6776534</v>
       </c>
       <c r="B3" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>504</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -841,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>500329.6358349703</v>
+        <v>500743</v>
       </c>
       <c r="R3" t="n">
-        <v>7026347.022219554</v>
+        <v>7026479</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,24 +849,14 @@
           <t>2012-09-10</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2012-09-10</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>på och vid gammal basväg</t>
+          <t>några plantor i rikkärrskant</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,11 +867,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Tallskog - barrblandskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -927,37 +887,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1869487</v>
+        <v>6776535</v>
       </c>
       <c r="B4" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>504</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -967,13 +922,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>500735.3437825085</v>
+        <v>500736</v>
       </c>
       <c r="R4" t="n">
-        <v>7026456.124031644</v>
+        <v>7026499</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1000,24 +955,14 @@
           <t>2012-09-10</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2012-09-10</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>sparsamt</t>
+          <t>1 best. ca 10 pl.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1028,11 +973,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Blandsumpskog - rikkärr</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1053,15 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1208310</v>
+        <v>6776536</v>
       </c>
       <c r="B5" t="n">
-        <v>85198</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1069,21 +1004,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3624</v>
+        <v>504</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff. : Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1093,10 +1028,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>500421.7671810306</v>
+        <v>500732</v>
       </c>
       <c r="R5" t="n">
-        <v>7026184.14754188</v>
+        <v>7026498</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1126,19 +1061,14 @@
           <t>2012-09-10</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2012-09-10</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>1 best. ca 10 pl.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1149,11 +1079,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Tallskog - barrblandskog</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1174,15 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>4899153</v>
+        <v>1161247</v>
       </c>
       <c r="B6" t="n">
-        <v>97308</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1190,21 +1110,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222467</v>
+        <v>3215</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gräsull</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Eriophorum latifolium</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Hoppe</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1214,10 +1134,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>500742.9766027589</v>
+        <v>500734</v>
       </c>
       <c r="R6" t="n">
-        <v>7026479.009090708</v>
+        <v>7026503</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1247,19 +1167,9 @@
           <t>2012-09-10</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2012-09-10</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1295,15 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>4964591</v>
+        <v>1208310</v>
       </c>
       <c r="B7" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87412</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1311,23 +1216,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>3624</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1335,10 +1236,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>500395.683780521</v>
+        <v>500422</v>
       </c>
       <c r="R7" t="n">
-        <v>7026360.042223946</v>
+        <v>7026184</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1368,24 +1269,9 @@
           <t>2012-09-10</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2012-09-10</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>nära Källbäcken</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1421,15 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>4964590</v>
+        <v>1208311</v>
       </c>
       <c r="B8" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87412</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,23 +1318,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>3624</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1461,10 +1338,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>500392.0874507745</v>
+        <v>500435</v>
       </c>
       <c r="R8" t="n">
-        <v>7026374.849083297</v>
+        <v>7026139</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1494,24 +1371,9 @@
           <t>2012-09-10</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2012-09-10</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>vid Källbäcken</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1550,12 +1412,7 @@
         <v>1256195</v>
       </c>
       <c r="B9" t="n">
-        <v>86320</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89035</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1567,7 +1424,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vit vaxskivling</t>
+          <t>Vitvaxing agg.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1583,10 +1440,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>500715.5826337038</v>
+        <v>500716</v>
       </c>
       <c r="R9" t="n">
-        <v>7026419.775161677</v>
+        <v>7026420</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1616,19 +1473,9 @@
           <t>2012-09-10</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2012-09-10</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1669,37 +1516,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1208311</v>
+        <v>1869486</v>
       </c>
       <c r="B10" t="n">
-        <v>85198</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3624</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schaeff. : Fr.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1709,13 +1551,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>500435.2534577968</v>
+        <v>500519</v>
       </c>
       <c r="R10" t="n">
-        <v>7026139.275862872</v>
+        <v>7026330</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1742,19 +1584,14 @@
           <t>2012-09-10</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2012-09-10</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>sparsamt på ett par granar</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1790,19 +1627,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1869486</v>
+        <v>1869487</v>
       </c>
       <c r="B11" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1830,10 +1662,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>500518.8009875695</v>
+        <v>500735</v>
       </c>
       <c r="R11" t="n">
-        <v>7026329.547553229</v>
+        <v>7026456</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1863,24 +1695,14 @@
           <t>2012-09-10</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2012-09-10</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>sparsamt på ett par granar</t>
+          <t>sparsamt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1894,7 +1716,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Tallskog - barrblandskog</t>
+          <t>Blandsumpskog - rikkärr</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1916,53 +1738,53 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>91488972</v>
+        <v>115229281</v>
       </c>
       <c r="B12" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Jämtland, Jmt</t>
+          <t>Slåttmyren, Slåttmyren, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>500601.0174712259</v>
+        <v>501010</v>
       </c>
       <c r="R12" t="n">
-        <v>7026377.124967736</v>
+        <v>7026103</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1986,22 +1808,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2018-07-01</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2018-10-31</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-03-17</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2016,66 +1833,62 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Schill</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Joel Schill</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>6776536</v>
+        <v>115229440</v>
       </c>
       <c r="B13" t="n">
-        <v>96239</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>504</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Slåttmyren / N /, norr om Örån, ca 1 km norr om Strangellsbodarna,, Jmt</t>
+          <t>Slåttmyren, Slåttmyren, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>500731.739846768</v>
+        <v>501041</v>
       </c>
       <c r="R13" t="n">
-        <v>7026497.851453799</v>
+        <v>7026164</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2102,27 +1915,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2012-09-10</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2012-09-10</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>1 best. ca 10 pl.</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2137,66 +1935,62 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Bodil Carlsson</t>
+          <t>Joel Schill</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bengt Petterson</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>Åtgärdsprogram för hotade arter</t>
-        </is>
-      </c>
+          <t>Joel Schill</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>6776535</v>
+        <v>115229743</v>
       </c>
       <c r="B14" t="n">
-        <v>96239</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>504</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Slåttmyren / N /, norr om Örån, ca 1 km norr om Strangellsbodarna,, Jmt</t>
+          <t>Slåttmyren, Slåttmyren, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>500735.7831976977</v>
+        <v>500980</v>
       </c>
       <c r="R14" t="n">
-        <v>7026499.198442719</v>
+        <v>7026149</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2223,27 +2017,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2012-09-10</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2012-09-10</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>1 best. ca 10 pl.</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2258,31 +2037,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Bodil Carlsson</t>
+          <t>Joel Schill</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Bengt Petterson</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>Åtgärdsprogram för hotade arter</t>
-        </is>
-      </c>
+          <t>Joel Schill</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>6776534</v>
+        <v>115230124</v>
       </c>
       <c r="B15" t="n">
-        <v>96239</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2290,34 +2060,49 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>504</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Slåttmyren / N /, norr om Örån, ca 1 km norr om Strangellsbodarna,, Jmt</t>
+          <t>Slåttmyren, Slåttmyren, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>500742.9766027589</v>
+        <v>500910</v>
       </c>
       <c r="R15" t="n">
-        <v>7026479.009090708</v>
+        <v>7025978</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2344,27 +2129,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2012-09-10</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2012-09-10</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>några plantor i rikkärrskant</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2379,31 +2149,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Bodil Carlsson</t>
+          <t>Joel Schill</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Bengt Petterson</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>Åtgärdsprogram för hotade arter</t>
-        </is>
-      </c>
+          <t>Joel Schill</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>6776533</v>
+        <v>115230930</v>
       </c>
       <c r="B16" t="n">
-        <v>96239</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2411,34 +2172,53 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>504</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Slåttmyren / N /, norr om Örån, ca 1 km norr om Strangellsbodarna,, Jmt</t>
+          <t>Våttjärnen, Våttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>500735.3437825085</v>
+        <v>500154</v>
       </c>
       <c r="R16" t="n">
-        <v>7026456.124031644</v>
+        <v>7026253</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2465,27 +2245,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2012-09-10</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2012-09-10</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>6 bestånd, totalt ca 50 pl. inom ca 100 m2.</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2500,31 +2265,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Bodil Carlsson</t>
+          <t>Joel Schill</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Bengt Petterson</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>Åtgärdsprogram för hotade arter</t>
-        </is>
-      </c>
+          <t>Joel Schill</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>115229281</v>
+        <v>115230295</v>
       </c>
       <c r="B17" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2532,39 +2288,43 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Slåttmyren (Slåttmyren), Jmt</t>
+          <t>Slåttmyren, Slåttmyren, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>501010</v>
+        <v>500700</v>
       </c>
       <c r="R17" t="n">
-        <v>7026103</v>
+        <v>7026044</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2597,11 +2357,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-03-17</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2628,15 +2383,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>115229743</v>
+        <v>115230735</v>
       </c>
       <c r="B18" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2644,39 +2394,43 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Slåttmyren (Slåttmyren), Jmt</t>
+          <t>Våttjärnen, Våttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>500980</v>
+        <v>500399</v>
       </c>
       <c r="R18" t="n">
-        <v>7026149</v>
+        <v>7026304</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2735,15 +2489,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>115230295</v>
+        <v>115230949</v>
       </c>
       <c r="B19" t="n">
-        <v>57414</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2770,7 +2519,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2780,14 +2529,14 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Slåttmyren (Slåttmyren), Jmt</t>
+          <t>Våttjärnen, Våttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>500700</v>
+        <v>500148</v>
       </c>
       <c r="R19" t="n">
-        <v>7026044</v>
+        <v>7026256</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2846,15 +2595,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>115230124</v>
+        <v>4899152</v>
       </c>
       <c r="B20" t="n">
-        <v>56478</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100143</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2862,49 +2606,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>222467</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gräsull</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Eriophorum latifolium</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Hoppe</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Slåttmyren (Slåttmyren), Jmt</t>
+          <t>Slåttmyren / N /, norr om Örån, ca 1 km norr om Strangellsbodarna,, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>500910</v>
+        <v>500163</v>
       </c>
       <c r="R20" t="n">
-        <v>7025978</v>
+        <v>7026264</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2931,12 +2660,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2012-09-10</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2012-09-10</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>rikkärrskant</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2947,75 +2681,70 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Tallskog - barrblandskog</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Joel Schill</t>
+          <t>Bodil Carlsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Joel Schill</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
+          <t>Bengt Petterson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Åtgärdsprogram för hotade arter</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>115230735</v>
+        <v>4899153</v>
       </c>
       <c r="B21" t="n">
-        <v>57414</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100143</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>222467</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gräsull</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Eriophorum latifolium</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>Hoppe</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Våttjärnen (Våttjärnen), Jmt</t>
+          <t>Slåttmyren / N /, norr om Örån, ca 1 km norr om Strangellsbodarna,, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>500399</v>
+        <v>500743</v>
       </c>
       <c r="R21" t="n">
-        <v>7026304</v>
+        <v>7026479</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3042,12 +2771,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2012-09-10</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2012-09-10</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3058,19 +2787,462 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Blandsumpskog - rikkärr</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Joel Schill</t>
+          <t>Bodil Carlsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Joel Schill</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
+          <t>Bengt Petterson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Åtgärdsprogram för hotade arter</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>4964589</v>
+      </c>
+      <c r="B22" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Slåttmyren / N /, norr om Örån, ca 1 km norr om Strangellsbodarna,, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>500330</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7026347</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2012-09-10</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2012-09-10</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>på och vid gammal basväg</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Tallskog - barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Bodil Carlsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Bengt Petterson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Åtgärdsprogram för hotade arter</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>4964590</v>
+      </c>
+      <c r="B23" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Slåttmyren / N /, norr om Örån, ca 1 km norr om Strangellsbodarna,, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>500392</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7026375</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2012-09-10</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2012-09-10</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>vid Källbäcken</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Tallskog - barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Bodil Carlsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Bengt Petterson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Åtgärdsprogram för hotade arter</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>4964591</v>
+      </c>
+      <c r="B24" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Slåttmyren / N /, norr om Örån, ca 1 km norr om Strangellsbodarna,, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>500396</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7026360</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2012-09-10</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2012-09-10</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>nära Källbäcken</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Tallskog - barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Bodil Carlsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Bengt Petterson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Åtgärdsprogram för hotade arter</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>91488972</v>
+      </c>
+      <c r="B25" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Jämtland, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>500601</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7026377</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2018-07-01</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2018-10-31</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 45224-2024 artfynd.xlsx
+++ b/artfynd/A 45224-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AZ25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115230930</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115230949</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4899152</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1111,6 +1131,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6776533</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1217,6 +1242,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6776534</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1323,6 +1353,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6776535</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1429,6 +1464,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6776536</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1535,6 +1575,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1161247</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1637,6 +1682,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1208310</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1739,6 +1789,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1208311</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1846,6 +1901,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1256195</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1957,6 +2017,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1869486</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2068,6 +2133,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1869487</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2175,6 +2245,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115229281</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2277,6 +2352,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115229440</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2379,6 +2459,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115229743</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2491,6 +2576,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115230124</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2597,6 +2687,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115230295</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2703,6 +2798,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115230735</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2809,6 +2909,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4899153</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2920,6 +3025,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4964589</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3031,6 +3141,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4964590</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3142,6 +3257,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4964591</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3243,8 +3363,39 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91488972</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>